--- a/temp_tp.xlsx
+++ b/temp_tp.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004169E1"/>
+        <bgColor rgb="004169E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3D3D3"/>
+        <bgColor rgb="00D3D3D3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +68,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,232 +447,348 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9.289999999999999" customWidth="1" min="1" max="1"/>
+    <col width="6.29" customWidth="1" min="2" max="2"/>
+    <col width="11.29" customWidth="1" min="3" max="3"/>
+    <col width="4.29" customWidth="1" min="4" max="4"/>
+    <col width="4.29" customWidth="1" min="5" max="5"/>
+    <col width="4.29" customWidth="1" min="6" max="6"/>
+    <col width="8.289999999999999" customWidth="1" min="7" max="7"/>
+    <col width="4.29" customWidth="1" min="8" max="8"/>
+    <col width="4.29" customWidth="1" min="9" max="9"/>
+    <col width="4.29" customWidth="1" min="10" max="10"/>
+    <col width="4.29" customWidth="1" min="11" max="11"/>
+    <col width="24.29" customWidth="1" min="12" max="12"/>
+    <col width="4.29" customWidth="1" min="13" max="13"/>
+    <col width="4.29" customWidth="1" min="14" max="14"/>
+    <col width="13.29" customWidth="1" min="15" max="15"/>
+    <col width="4.29" customWidth="1" min="16" max="16"/>
+    <col width="7.29" customWidth="1" min="17" max="17"/>
+    <col width="4.29" customWidth="1" min="18" max="18"/>
+    <col width="9.289999999999999" customWidth="1" min="19" max="19"/>
+    <col width="13.29" customWidth="1" min="20" max="20"/>
+    <col width="9.289999999999999" customWidth="1" min="21" max="21"/>
+    <col width="9.289999999999999" customWidth="1" min="22" max="22"/>
+    <col width="4.29" customWidth="1" min="23" max="23"/>
+    <col width="4.29" customWidth="1" min="24" max="24"/>
+    <col width="4.29" customWidth="1" min="25" max="25"/>
+    <col width="4.29" customWidth="1" min="26" max="26"/>
+    <col width="12.29" customWidth="1" min="27" max="27"/>
+    <col width="11.29" customWidth="1" min="28" max="28"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data de Emissão NL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>UG Emitente</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nota de Empenho</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Tipo Patrimonial</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Item Patrimonial</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Operação Patrimonial</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valor do Item</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Tipo de Retenção</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Credor da Retenção</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Valor da Base de Cálculo da Retenção</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Valor da Retenção</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Mês de Competência</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Data do Processo</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Código do Processo</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Credor Secundário</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>DEA</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Tipo de Documento Comprobatório</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Número Documento Comprobatório</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Processo Documento Comprobatório</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Data Documento Comprobatório</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Competência Documento Comprobatório</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Tipo de Série Documento Comprobatório</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Descrição Tipo de Série Documento Comprobatório</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Chave de Acesso Documento Comprobatório</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Código de Verificação Documento Comprobatório</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Valor Documento Comprobatório</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Categoria do PADV</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>390000</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>2026NE032824</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>1902</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SESP/DEPPEN - PAGAMENTO DE EXTRAJORNADA – REF. 07/2026 - REGIONAL DE UMUARAMA</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>252522</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>SESP/DEPPEN - PAGAMENTO DE EXTRAJORNADA – REF. 06/2026 - REGIONAL DE UMUARAMA</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>26.214.012-1</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>252522</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>26.214.012-1</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026NE032825</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1902</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>SESP/DEPPEN - PAGAMENTO DE EXTRAJORNADA – REF. 06/2026 - REGIONAL DE UMUARAMA</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>26.214.012-1</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>26.214.012-1</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/temp_tp.xlsx
+++ b/temp_tp.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.289999999999999" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026NE032824</t>
+          <t>2026NE032823</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -663,7 +663,7 @@
       <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>26.214.012-1</t>
+          <t>252</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>26.214.012-1</t>
+          <t>252</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026NE032825</t>
+          <t>2026NE032830</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -730,7 +730,7 @@
         <v>58</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
@@ -747,7 +747,7 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>26.214.012-1</t>
+          <t>252</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>26.214.012-1</t>
+          <t>252</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -786,9 +786,177 @@
       <c r="Y3" s="3" t="inlineStr"/>
       <c r="Z3" s="3" t="inlineStr"/>
       <c r="AA3" s="3" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="AB3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026NE032836</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1902</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>540</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>SESP/DEPPEN - PAGAMENTO DE EXTRAJORNADA – REF. 06/2026 - REGIONAL DE UMUARAMA</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026NE032918</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1902</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>SESP/DEPPEN - PAGAMENTO DE EXTRAJORNADA – REF. 06/2026 - REGIONAL DE UMUARAMA</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/temp_tp.xlsx
+++ b/temp_tp.xlsx
@@ -663,7 +663,7 @@
       <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -747,7 +747,7 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -898,7 +898,7 @@
         <v>58</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       <c r="Y5" s="3" t="inlineStr"/>
       <c r="Z5" s="3" t="inlineStr"/>
       <c r="AA5" s="3" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="AB5" s="3" t="inlineStr"/>
     </row>
